--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515906</v>
+        <v>121515901</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>77948</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593300</v>
+        <v>593507</v>
       </c>
       <c r="R2" t="n">
-        <v>7183536</v>
+        <v>7183619</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515902</v>
+        <v>121515899</v>
       </c>
       <c r="B3" t="n">
-        <v>82391</v>
+        <v>97052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593507</v>
+        <v>593510</v>
       </c>
       <c r="R3" t="n">
-        <v>7183619</v>
+        <v>7183602</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515898</v>
+        <v>121515902</v>
       </c>
       <c r="B4" t="n">
-        <v>90731</v>
+        <v>82391</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593511</v>
+        <v>593507</v>
       </c>
       <c r="R4" t="n">
-        <v>7183603</v>
+        <v>7183619</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515896</v>
+        <v>121515907</v>
       </c>
       <c r="B6" t="n">
         <v>57354</v>
@@ -1159,7 +1159,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593511</v>
+        <v>593287</v>
       </c>
       <c r="R6" t="n">
-        <v>7183604</v>
+        <v>7183515</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515899</v>
+        <v>121515905</v>
       </c>
       <c r="B7" t="n">
-        <v>97052</v>
+        <v>90731</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,25 +1252,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593510</v>
+        <v>593297</v>
       </c>
       <c r="R7" t="n">
-        <v>7183602</v>
+        <v>7183540</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515905</v>
+        <v>121515909</v>
       </c>
       <c r="B8" t="n">
         <v>90731</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593297</v>
+        <v>593312</v>
       </c>
       <c r="R8" t="n">
-        <v>7183540</v>
+        <v>7183526</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515913</v>
+        <v>121515894</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,34 +1480,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593494</v>
+        <v>593555</v>
       </c>
       <c r="R9" t="n">
-        <v>7183555</v>
+        <v>7183567</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515912</v>
+        <v>121515903</v>
       </c>
       <c r="B10" t="n">
-        <v>57370</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,39 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593492</v>
+        <v>593507</v>
       </c>
       <c r="R10" t="n">
-        <v>7183557</v>
+        <v>7183619</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515909</v>
+        <v>121515912</v>
       </c>
       <c r="B11" t="n">
-        <v>90731</v>
+        <v>57370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,34 +1709,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593312</v>
+        <v>593492</v>
       </c>
       <c r="R11" t="n">
-        <v>7183526</v>
+        <v>7183557</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1917,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515903</v>
+        <v>121515898</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593507</v>
+        <v>593511</v>
       </c>
       <c r="R13" t="n">
-        <v>7183619</v>
+        <v>7183603</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515895</v>
+        <v>121515896</v>
       </c>
       <c r="B14" t="n">
-        <v>57370</v>
+        <v>57354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,16 +2050,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2074,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593515</v>
+        <v>593511</v>
       </c>
       <c r="R14" t="n">
-        <v>7183592</v>
+        <v>7183604</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2146,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515894</v>
+        <v>121515906</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,39 +2167,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593555</v>
+        <v>593300</v>
       </c>
       <c r="R15" t="n">
-        <v>7183567</v>
+        <v>7183536</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515907</v>
+        <v>121515895</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>57370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,16 +2279,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2299,7 +2299,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593287</v>
+        <v>593515</v>
       </c>
       <c r="R16" t="n">
-        <v>7183515</v>
+        <v>7183592</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515904</v>
+        <v>121515913</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,39 +2396,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593316</v>
+        <v>593494</v>
       </c>
       <c r="R17" t="n">
-        <v>7183542</v>
+        <v>7183555</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515901</v>
+        <v>121515904</v>
       </c>
       <c r="B18" t="n">
-        <v>77948</v>
+        <v>57354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,38 +2504,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593507</v>
+        <v>593316</v>
       </c>
       <c r="R18" t="n">
-        <v>7183619</v>
+        <v>7183542</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515912</v>
+        <v>121515898</v>
       </c>
       <c r="B11" t="n">
-        <v>57370</v>
+        <v>90731</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,39 +1709,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593492</v>
+        <v>593511</v>
       </c>
       <c r="R11" t="n">
-        <v>7183557</v>
+        <v>7183603</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515911</v>
+        <v>121515912</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>57370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,34 +1821,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593312</v>
+        <v>593492</v>
       </c>
       <c r="R12" t="n">
-        <v>7183527</v>
+        <v>7183557</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515898</v>
+        <v>121515911</v>
       </c>
       <c r="B13" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593511</v>
+        <v>593312</v>
       </c>
       <c r="R13" t="n">
-        <v>7183603</v>
+        <v>7183527</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515901</v>
+        <v>121515911</v>
       </c>
       <c r="B2" t="n">
-        <v>77948</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593507</v>
+        <v>593312</v>
       </c>
       <c r="R2" t="n">
-        <v>7183619</v>
+        <v>7183527</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515899</v>
+        <v>121515912</v>
       </c>
       <c r="B3" t="n">
-        <v>97052</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593510</v>
+        <v>593492</v>
       </c>
       <c r="R3" t="n">
-        <v>7183602</v>
+        <v>7183557</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515902</v>
+        <v>121515900</v>
       </c>
       <c r="B4" t="n">
-        <v>82391</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593507</v>
+        <v>593510</v>
       </c>
       <c r="R4" t="n">
-        <v>7183619</v>
+        <v>7183600</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515900</v>
+        <v>121515904</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593510</v>
+        <v>593316</v>
       </c>
       <c r="R5" t="n">
-        <v>7183600</v>
+        <v>7183542</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515907</v>
+        <v>121515906</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593287</v>
+        <v>593300</v>
       </c>
       <c r="R6" t="n">
-        <v>7183515</v>
+        <v>7183536</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515905</v>
+        <v>121515909</v>
       </c>
       <c r="B7" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593297</v>
+        <v>593312</v>
       </c>
       <c r="R7" t="n">
-        <v>7183540</v>
+        <v>7183526</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515909</v>
+        <v>121515903</v>
       </c>
       <c r="B8" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593312</v>
+        <v>593507</v>
       </c>
       <c r="R8" t="n">
-        <v>7183526</v>
+        <v>7183619</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515894</v>
+        <v>121515898</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,39 +1485,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593555</v>
+        <v>593511</v>
       </c>
       <c r="R9" t="n">
-        <v>7183567</v>
+        <v>7183603</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515903</v>
+        <v>121515901</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>77949</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,25 +1593,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515898</v>
+        <v>121515896</v>
       </c>
       <c r="B11" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,24 +1709,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -1736,7 +1741,7 @@
         <v>593511</v>
       </c>
       <c r="R11" t="n">
-        <v>7183603</v>
+        <v>7183604</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1805,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515912</v>
+        <v>121515899</v>
       </c>
       <c r="B12" t="n">
-        <v>57370</v>
+        <v>97058</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,43 +1822,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593492</v>
+        <v>593510</v>
       </c>
       <c r="R12" t="n">
-        <v>7183557</v>
+        <v>7183602</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515911</v>
+        <v>121515913</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593312</v>
+        <v>593494</v>
       </c>
       <c r="R13" t="n">
-        <v>7183527</v>
+        <v>7183555</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515896</v>
+        <v>121515895</v>
       </c>
       <c r="B14" t="n">
-        <v>57354</v>
+        <v>57371</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,16 +2050,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593511</v>
+        <v>593515</v>
       </c>
       <c r="R14" t="n">
-        <v>7183604</v>
+        <v>7183592</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515906</v>
+        <v>121515894</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,34 +2167,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593300</v>
+        <v>593555</v>
       </c>
       <c r="R15" t="n">
-        <v>7183536</v>
+        <v>7183567</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515895</v>
+        <v>121515907</v>
       </c>
       <c r="B16" t="n">
-        <v>57370</v>
+        <v>57355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,16 +2284,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2299,7 +2304,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2308,10 +2313,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593515</v>
+        <v>593287</v>
       </c>
       <c r="R16" t="n">
-        <v>7183592</v>
+        <v>7183515</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515913</v>
+        <v>121515902</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>82392</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,21 +2401,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2420,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593494</v>
+        <v>593507</v>
       </c>
       <c r="R17" t="n">
-        <v>7183555</v>
+        <v>7183619</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515904</v>
+        <v>121515905</v>
       </c>
       <c r="B18" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,39 +2513,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593316</v>
+        <v>593297</v>
       </c>
       <c r="R18" t="n">
-        <v>7183542</v>
+        <v>7183540</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515911</v>
+        <v>121515906</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593312</v>
+        <v>593300</v>
       </c>
       <c r="R2" t="n">
-        <v>7183527</v>
+        <v>7183536</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515912</v>
+        <v>121515905</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593492</v>
+        <v>593297</v>
       </c>
       <c r="R3" t="n">
-        <v>7183557</v>
+        <v>7183540</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515900</v>
+        <v>121515894</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593510</v>
+        <v>593555</v>
       </c>
       <c r="R4" t="n">
-        <v>7183600</v>
+        <v>7183567</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515904</v>
+        <v>121515895</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1052,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593316</v>
+        <v>593515</v>
       </c>
       <c r="R5" t="n">
-        <v>7183542</v>
+        <v>7183592</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515906</v>
+        <v>121515903</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593300</v>
+        <v>593507</v>
       </c>
       <c r="R6" t="n">
-        <v>7183536</v>
+        <v>7183619</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515909</v>
+        <v>121515907</v>
       </c>
       <c r="B7" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593312</v>
+        <v>593287</v>
       </c>
       <c r="R7" t="n">
-        <v>7183526</v>
+        <v>7183515</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515903</v>
+        <v>121515896</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1378,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593507</v>
+        <v>593511</v>
       </c>
       <c r="R8" t="n">
-        <v>7183619</v>
+        <v>7183604</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515898</v>
+        <v>121515902</v>
       </c>
       <c r="B9" t="n">
-        <v>90737</v>
+        <v>82393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593511</v>
+        <v>593507</v>
       </c>
       <c r="R9" t="n">
-        <v>7183603</v>
+        <v>7183619</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515901</v>
+        <v>121515913</v>
       </c>
       <c r="B10" t="n">
-        <v>77949</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,25 +1603,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593507</v>
+        <v>593494</v>
       </c>
       <c r="R10" t="n">
-        <v>7183619</v>
+        <v>7183555</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515896</v>
+        <v>121515898</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,29 +1719,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -1741,7 +1746,7 @@
         <v>593511</v>
       </c>
       <c r="R11" t="n">
-        <v>7183604</v>
+        <v>7183603</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1810,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515899</v>
+        <v>121515911</v>
       </c>
       <c r="B12" t="n">
-        <v>97058</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,25 +1827,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593510</v>
+        <v>593312</v>
       </c>
       <c r="R12" t="n">
-        <v>7183602</v>
+        <v>7183527</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515913</v>
+        <v>121515904</v>
       </c>
       <c r="B13" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,34 +1943,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593494</v>
+        <v>593316</v>
       </c>
       <c r="R13" t="n">
-        <v>7183555</v>
+        <v>7183542</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515895</v>
+        <v>121515912</v>
       </c>
       <c r="B14" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,7 +2080,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2079,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593515</v>
+        <v>593492</v>
       </c>
       <c r="R14" t="n">
-        <v>7183592</v>
+        <v>7183557</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515894</v>
+        <v>121515901</v>
       </c>
       <c r="B15" t="n">
-        <v>57355</v>
+        <v>77950</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2163,43 +2173,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593555</v>
+        <v>593507</v>
       </c>
       <c r="R15" t="n">
-        <v>7183567</v>
+        <v>7183619</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515907</v>
+        <v>121515909</v>
       </c>
       <c r="B16" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,39 +2289,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593287</v>
+        <v>593312</v>
       </c>
       <c r="R16" t="n">
-        <v>7183515</v>
+        <v>7183526</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515902</v>
+        <v>121515899</v>
       </c>
       <c r="B17" t="n">
-        <v>82392</v>
+        <v>97059</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2397,25 +2397,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593507</v>
+        <v>593510</v>
       </c>
       <c r="R17" t="n">
-        <v>7183619</v>
+        <v>7183602</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515905</v>
+        <v>121515900</v>
       </c>
       <c r="B18" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,21 +2513,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593297</v>
+        <v>593510</v>
       </c>
       <c r="R18" t="n">
-        <v>7183540</v>
+        <v>7183600</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515906</v>
+        <v>121515907</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593300</v>
+        <v>593287</v>
       </c>
       <c r="R2" t="n">
-        <v>7183536</v>
+        <v>7183515</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515905</v>
+        <v>121515898</v>
       </c>
       <c r="B3" t="n">
         <v>90738</v>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593297</v>
+        <v>593511</v>
       </c>
       <c r="R3" t="n">
-        <v>7183540</v>
+        <v>7183603</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515894</v>
+        <v>121515900</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593555</v>
+        <v>593510</v>
       </c>
       <c r="R4" t="n">
-        <v>7183567</v>
+        <v>7183600</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515895</v>
+        <v>121515904</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1052,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593515</v>
+        <v>593316</v>
       </c>
       <c r="R5" t="n">
-        <v>7183592</v>
+        <v>7183542</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515903</v>
+        <v>121515895</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593507</v>
+        <v>593515</v>
       </c>
       <c r="R6" t="n">
-        <v>7183619</v>
+        <v>7183592</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515907</v>
+        <v>121515899</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,43 +1262,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593287</v>
+        <v>593510</v>
       </c>
       <c r="R7" t="n">
-        <v>7183515</v>
+        <v>7183602</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515896</v>
+        <v>121515902</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,39 +1378,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593511</v>
+        <v>593507</v>
       </c>
       <c r="R8" t="n">
-        <v>7183604</v>
+        <v>7183619</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515902</v>
+        <v>121515912</v>
       </c>
       <c r="B9" t="n">
-        <v>82393</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,34 +1490,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593507</v>
+        <v>593492</v>
       </c>
       <c r="R9" t="n">
-        <v>7183619</v>
+        <v>7183557</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515913</v>
+        <v>121515896</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,34 +1607,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593494</v>
+        <v>593511</v>
       </c>
       <c r="R10" t="n">
-        <v>7183555</v>
+        <v>7183604</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515898</v>
+        <v>121515901</v>
       </c>
       <c r="B11" t="n">
-        <v>90738</v>
+        <v>77950</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,25 +1720,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593511</v>
+        <v>593507</v>
       </c>
       <c r="R11" t="n">
-        <v>7183603</v>
+        <v>7183619</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,7 +1820,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515911</v>
+        <v>121515913</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1855,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593312</v>
+        <v>593494</v>
       </c>
       <c r="R12" t="n">
-        <v>7183527</v>
+        <v>7183555</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515904</v>
+        <v>121515906</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,39 +1948,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593316</v>
+        <v>593300</v>
       </c>
       <c r="R13" t="n">
-        <v>7183542</v>
+        <v>7183536</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515912</v>
+        <v>121515911</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,39 +2060,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593492</v>
+        <v>593312</v>
       </c>
       <c r="R14" t="n">
-        <v>7183557</v>
+        <v>7183527</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2124,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515901</v>
+        <v>121515909</v>
       </c>
       <c r="B15" t="n">
-        <v>77950</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,25 +2168,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2201,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593507</v>
+        <v>593312</v>
       </c>
       <c r="R15" t="n">
-        <v>7183619</v>
+        <v>7183526</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2236,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,7 +2268,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515909</v>
+        <v>121515905</v>
       </c>
       <c r="B16" t="n">
         <v>90738</v>
@@ -2313,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593312</v>
+        <v>593297</v>
       </c>
       <c r="R16" t="n">
-        <v>7183526</v>
+        <v>7183540</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2348,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515899</v>
+        <v>121515894</v>
       </c>
       <c r="B17" t="n">
-        <v>97059</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2397,38 +2392,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593510</v>
+        <v>593555</v>
       </c>
       <c r="R17" t="n">
-        <v>7183602</v>
+        <v>7183567</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,7 +2497,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515900</v>
+        <v>121515903</v>
       </c>
       <c r="B18" t="n">
         <v>78609</v>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593510</v>
+        <v>593507</v>
       </c>
       <c r="R18" t="n">
-        <v>7183600</v>
+        <v>7183619</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515907</v>
+        <v>121515906</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593287</v>
+        <v>593300</v>
       </c>
       <c r="R2" t="n">
-        <v>7183515</v>
+        <v>7183536</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515898</v>
+        <v>121515904</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593511</v>
+        <v>593316</v>
       </c>
       <c r="R3" t="n">
-        <v>7183603</v>
+        <v>7183542</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515900</v>
+        <v>121515901</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>77950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593510</v>
+        <v>593507</v>
       </c>
       <c r="R4" t="n">
-        <v>7183600</v>
+        <v>7183619</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515904</v>
+        <v>121515909</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593316</v>
+        <v>593312</v>
       </c>
       <c r="R5" t="n">
-        <v>7183542</v>
+        <v>7183526</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515895</v>
+        <v>121515900</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593515</v>
+        <v>593510</v>
       </c>
       <c r="R6" t="n">
-        <v>7183592</v>
+        <v>7183600</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515899</v>
+        <v>121515896</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,38 +1252,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593510</v>
+        <v>593511</v>
       </c>
       <c r="R7" t="n">
-        <v>7183602</v>
+        <v>7183604</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515902</v>
+        <v>121515913</v>
       </c>
       <c r="B8" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593507</v>
+        <v>593494</v>
       </c>
       <c r="R8" t="n">
-        <v>7183619</v>
+        <v>7183555</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515912</v>
+        <v>121515902</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>82393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,39 +1485,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593492</v>
+        <v>593507</v>
       </c>
       <c r="R9" t="n">
-        <v>7183557</v>
+        <v>7183619</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515896</v>
+        <v>121515907</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1627,7 +1617,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1636,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593511</v>
+        <v>593287</v>
       </c>
       <c r="R10" t="n">
-        <v>7183604</v>
+        <v>7183515</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515901</v>
+        <v>121515899</v>
       </c>
       <c r="B11" t="n">
-        <v>77950</v>
+        <v>97059</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,25 +1710,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>498</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593507</v>
+        <v>593510</v>
       </c>
       <c r="R11" t="n">
-        <v>7183619</v>
+        <v>7183602</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1820,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515913</v>
+        <v>121515894</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593494</v>
+        <v>593555</v>
       </c>
       <c r="R12" t="n">
-        <v>7183555</v>
+        <v>7183567</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,7 +1927,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515906</v>
+        <v>121515903</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1972,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593300</v>
+        <v>593507</v>
       </c>
       <c r="R13" t="n">
-        <v>7183536</v>
+        <v>7183619</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2156,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515909</v>
+        <v>121515895</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,34 +2167,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593312</v>
+        <v>593515</v>
       </c>
       <c r="R15" t="n">
-        <v>7183526</v>
+        <v>7183592</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2380,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515894</v>
+        <v>121515912</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,16 +2396,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2416,7 +2416,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593555</v>
+        <v>593492</v>
       </c>
       <c r="R17" t="n">
-        <v>7183567</v>
+        <v>7183557</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515903</v>
+        <v>121515898</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,21 +2513,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593507</v>
+        <v>593511</v>
       </c>
       <c r="R18" t="n">
-        <v>7183619</v>
+        <v>7183603</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515906</v>
+        <v>121515902</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593300</v>
+        <v>593507</v>
       </c>
       <c r="R2" t="n">
-        <v>7183536</v>
+        <v>7183619</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515904</v>
+        <v>121515899</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593316</v>
+        <v>593510</v>
       </c>
       <c r="R3" t="n">
-        <v>7183542</v>
+        <v>7183602</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515901</v>
+        <v>121515898</v>
       </c>
       <c r="B4" t="n">
-        <v>77950</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593507</v>
+        <v>593511</v>
       </c>
       <c r="R4" t="n">
-        <v>7183619</v>
+        <v>7183603</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515909</v>
+        <v>121515903</v>
       </c>
       <c r="B5" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593312</v>
+        <v>593507</v>
       </c>
       <c r="R5" t="n">
-        <v>7183526</v>
+        <v>7183619</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515900</v>
+        <v>121515909</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593510</v>
+        <v>593312</v>
       </c>
       <c r="R6" t="n">
-        <v>7183600</v>
+        <v>7183526</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515896</v>
+        <v>121515911</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593511</v>
+        <v>593312</v>
       </c>
       <c r="R7" t="n">
-        <v>7183604</v>
+        <v>7183527</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1469,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515902</v>
+        <v>121515904</v>
       </c>
       <c r="B9" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593507</v>
+        <v>593316</v>
       </c>
       <c r="R9" t="n">
-        <v>7183619</v>
+        <v>7183542</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1698,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515899</v>
+        <v>121515912</v>
       </c>
       <c r="B11" t="n">
-        <v>97059</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,38 +1705,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593510</v>
+        <v>593492</v>
       </c>
       <c r="R11" t="n">
-        <v>7183602</v>
+        <v>7183557</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515903</v>
+        <v>121515901</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>77950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,25 +1939,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,7 +2039,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515911</v>
+        <v>121515900</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593312</v>
+        <v>593510</v>
       </c>
       <c r="R14" t="n">
-        <v>7183527</v>
+        <v>7183600</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515895</v>
+        <v>121515906</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,39 +2167,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593515</v>
+        <v>593300</v>
       </c>
       <c r="R15" t="n">
-        <v>7183592</v>
+        <v>7183536</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515905</v>
+        <v>121515895</v>
       </c>
       <c r="B16" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,34 +2279,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593297</v>
+        <v>593515</v>
       </c>
       <c r="R16" t="n">
-        <v>7183540</v>
+        <v>7183592</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515912</v>
+        <v>121515905</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,39 +2396,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593492</v>
+        <v>593297</v>
       </c>
       <c r="R17" t="n">
-        <v>7183557</v>
+        <v>7183540</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515898</v>
+        <v>121515896</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,24 +2508,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -2540,7 +2540,7 @@
         <v>593511</v>
       </c>
       <c r="R18" t="n">
-        <v>7183603</v>
+        <v>7183604</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515895</v>
+        <v>121515905</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>90738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,39 +2279,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593515</v>
+        <v>593297</v>
       </c>
       <c r="R16" t="n">
-        <v>7183592</v>
+        <v>7183540</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515905</v>
+        <v>121515895</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,34 +2391,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593297</v>
+        <v>593515</v>
       </c>
       <c r="R17" t="n">
-        <v>7183540</v>
+        <v>7183592</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515905</v>
+        <v>121515895</v>
       </c>
       <c r="B16" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,34 +2279,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593297</v>
+        <v>593515</v>
       </c>
       <c r="R16" t="n">
-        <v>7183540</v>
+        <v>7183592</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2338,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515895</v>
+        <v>121515905</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,39 +2396,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593515</v>
+        <v>593297</v>
       </c>
       <c r="R17" t="n">
-        <v>7183592</v>
+        <v>7183540</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515906</v>
+        <v>121515901</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>77957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593300</v>
+        <v>593507</v>
       </c>
       <c r="R2" t="n">
-        <v>7183536</v>
+        <v>7183619</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515911</v>
+        <v>121515896</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593312</v>
+        <v>593511</v>
       </c>
       <c r="R3" t="n">
-        <v>7183527</v>
+        <v>7183604</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515901</v>
+        <v>121515904</v>
       </c>
       <c r="B4" t="n">
-        <v>77957</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +916,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593507</v>
+        <v>593316</v>
       </c>
       <c r="R4" t="n">
-        <v>7183619</v>
+        <v>7183542</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515912</v>
+        <v>121515906</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593492</v>
+        <v>593300</v>
       </c>
       <c r="R5" t="n">
-        <v>7183557</v>
+        <v>7183536</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515899</v>
+        <v>121515913</v>
       </c>
       <c r="B6" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1145,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593510</v>
+        <v>593494</v>
       </c>
       <c r="R6" t="n">
-        <v>7183602</v>
+        <v>7183555</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515904</v>
+        <v>121515895</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,16 +1261,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1276,7 +1281,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1285,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593316</v>
+        <v>593515</v>
       </c>
       <c r="R7" t="n">
-        <v>7183542</v>
+        <v>7183592</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1581,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515909</v>
+        <v>121515894</v>
       </c>
       <c r="B10" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1602,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593312</v>
+        <v>593555</v>
       </c>
       <c r="R10" t="n">
-        <v>7183526</v>
+        <v>7183567</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515898</v>
+        <v>121515899</v>
       </c>
       <c r="B11" t="n">
-        <v>90746</v>
+        <v>97067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,25 +1715,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593511</v>
+        <v>593510</v>
       </c>
       <c r="R11" t="n">
-        <v>7183603</v>
+        <v>7183602</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,7 +1815,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515913</v>
+        <v>121515900</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1845,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593494</v>
+        <v>593510</v>
       </c>
       <c r="R12" t="n">
-        <v>7183555</v>
+        <v>7183600</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515896</v>
+        <v>121515912</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,16 +1943,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1953,7 +1963,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1962,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593511</v>
+        <v>593492</v>
       </c>
       <c r="R13" t="n">
-        <v>7183604</v>
+        <v>7183557</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515907</v>
+        <v>121515909</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,39 +2060,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593287</v>
+        <v>593312</v>
       </c>
       <c r="R14" t="n">
-        <v>7183515</v>
+        <v>7183526</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515895</v>
+        <v>121515898</v>
       </c>
       <c r="B15" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,39 +2172,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593515</v>
+        <v>593511</v>
       </c>
       <c r="R15" t="n">
-        <v>7183592</v>
+        <v>7183603</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2268,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515905</v>
+        <v>121515911</v>
       </c>
       <c r="B16" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593297</v>
+        <v>593312</v>
       </c>
       <c r="R16" t="n">
-        <v>7183540</v>
+        <v>7183527</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515900</v>
+        <v>121515905</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,21 +2396,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593510</v>
+        <v>593297</v>
       </c>
       <c r="R17" t="n">
-        <v>7183600</v>
+        <v>7183540</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,7 +2492,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515894</v>
+        <v>121515907</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2528,7 +2528,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593555</v>
+        <v>593287</v>
       </c>
       <c r="R18" t="n">
-        <v>7183567</v>
+        <v>7183515</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515901</v>
+        <v>121515896</v>
       </c>
       <c r="B2" t="n">
-        <v>77957</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593507</v>
+        <v>593511</v>
       </c>
       <c r="R2" t="n">
-        <v>7183619</v>
+        <v>7183604</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515896</v>
+        <v>121515901</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>77957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593511</v>
+        <v>593507</v>
       </c>
       <c r="R3" t="n">
-        <v>7183604</v>
+        <v>7183619</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515902</v>
+        <v>121515903</v>
       </c>
       <c r="B8" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515903</v>
+        <v>121515902</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515896</v>
+        <v>121515895</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593511</v>
+        <v>593515</v>
       </c>
       <c r="R2" t="n">
-        <v>7183604</v>
+        <v>7183592</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515901</v>
+        <v>121515906</v>
       </c>
       <c r="B3" t="n">
-        <v>77957</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593507</v>
+        <v>593300</v>
       </c>
       <c r="R3" t="n">
-        <v>7183619</v>
+        <v>7183536</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515904</v>
+        <v>121515901</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>77957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,43 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593316</v>
+        <v>593507</v>
       </c>
       <c r="R4" t="n">
-        <v>7183542</v>
+        <v>7183619</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515906</v>
+        <v>121515911</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1061,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593300</v>
+        <v>593312</v>
       </c>
       <c r="R5" t="n">
-        <v>7183536</v>
+        <v>7183527</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515913</v>
+        <v>121515894</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593494</v>
+        <v>593555</v>
       </c>
       <c r="R6" t="n">
-        <v>7183555</v>
+        <v>7183567</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515895</v>
+        <v>121515898</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593515</v>
+        <v>593511</v>
       </c>
       <c r="R7" t="n">
-        <v>7183592</v>
+        <v>7183603</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1362,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515903</v>
+        <v>121515913</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1402,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593507</v>
+        <v>593494</v>
       </c>
       <c r="R8" t="n">
-        <v>7183619</v>
+        <v>7183555</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515902</v>
+        <v>121515912</v>
       </c>
       <c r="B9" t="n">
-        <v>82400</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,34 +1485,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593507</v>
+        <v>593492</v>
       </c>
       <c r="R9" t="n">
-        <v>7183619</v>
+        <v>7183557</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515894</v>
+        <v>121515896</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593555</v>
+        <v>593511</v>
       </c>
       <c r="R10" t="n">
-        <v>7183567</v>
+        <v>7183604</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515899</v>
+        <v>121515900</v>
       </c>
       <c r="B11" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,25 +1715,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
         <v>593510</v>
       </c>
       <c r="R11" t="n">
-        <v>7183602</v>
+        <v>7183600</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515900</v>
+        <v>121515905</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593510</v>
+        <v>593297</v>
       </c>
       <c r="R12" t="n">
-        <v>7183600</v>
+        <v>7183540</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515912</v>
+        <v>121515904</v>
       </c>
       <c r="B13" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,16 +1943,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593492</v>
+        <v>593316</v>
       </c>
       <c r="R13" t="n">
-        <v>7183557</v>
+        <v>7183542</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515909</v>
+        <v>121515907</v>
       </c>
       <c r="B14" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,34 +2060,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593312</v>
+        <v>593287</v>
       </c>
       <c r="R14" t="n">
-        <v>7183526</v>
+        <v>7183515</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515898</v>
+        <v>121515903</v>
       </c>
       <c r="B15" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,21 +2177,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593511</v>
+        <v>593507</v>
       </c>
       <c r="R15" t="n">
-        <v>7183603</v>
+        <v>7183619</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515911</v>
+        <v>121515909</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,21 +2289,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2311,7 +2316,7 @@
         <v>593312</v>
       </c>
       <c r="R16" t="n">
-        <v>7183527</v>
+        <v>7183526</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2380,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515905</v>
+        <v>121515902</v>
       </c>
       <c r="B17" t="n">
-        <v>90746</v>
+        <v>82400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,21 +2401,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2420,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593297</v>
+        <v>593507</v>
       </c>
       <c r="R17" t="n">
-        <v>7183540</v>
+        <v>7183619</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515907</v>
+        <v>121515899</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>97067</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2504,43 +2509,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593287</v>
+        <v>593510</v>
       </c>
       <c r="R18" t="n">
-        <v>7183515</v>
+        <v>7183602</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515895</v>
+        <v>121515912</v>
       </c>
       <c r="B2" t="n">
         <v>57373</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593515</v>
+        <v>593492</v>
       </c>
       <c r="R2" t="n">
-        <v>7183592</v>
+        <v>7183557</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515906</v>
+        <v>121515895</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593300</v>
+        <v>593515</v>
       </c>
       <c r="R3" t="n">
-        <v>7183536</v>
+        <v>7183592</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515901</v>
+        <v>121515900</v>
       </c>
       <c r="B4" t="n">
-        <v>77957</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593507</v>
+        <v>593510</v>
       </c>
       <c r="R4" t="n">
-        <v>7183619</v>
+        <v>7183600</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515911</v>
+        <v>121515902</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593312</v>
+        <v>593507</v>
       </c>
       <c r="R5" t="n">
-        <v>7183527</v>
+        <v>7183619</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515894</v>
+        <v>121515906</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593555</v>
+        <v>593300</v>
       </c>
       <c r="R6" t="n">
-        <v>7183567</v>
+        <v>7183536</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515898</v>
+        <v>121515894</v>
       </c>
       <c r="B7" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593511</v>
+        <v>593555</v>
       </c>
       <c r="R7" t="n">
-        <v>7183603</v>
+        <v>7183567</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515913</v>
+        <v>121515899</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593494</v>
+        <v>593510</v>
       </c>
       <c r="R8" t="n">
-        <v>7183555</v>
+        <v>7183602</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515912</v>
+        <v>121515911</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,39 +1490,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593492</v>
+        <v>593312</v>
       </c>
       <c r="R9" t="n">
-        <v>7183557</v>
+        <v>7183527</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515896</v>
+        <v>121515905</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,39 +1602,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593511</v>
+        <v>593297</v>
       </c>
       <c r="R10" t="n">
-        <v>7183604</v>
+        <v>7183540</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515900</v>
+        <v>121515909</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593510</v>
+        <v>593312</v>
       </c>
       <c r="R11" t="n">
-        <v>7183600</v>
+        <v>7183526</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515905</v>
+        <v>121515907</v>
       </c>
       <c r="B12" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593297</v>
+        <v>593287</v>
       </c>
       <c r="R12" t="n">
-        <v>7183540</v>
+        <v>7183515</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515904</v>
+        <v>121515901</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>77957</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,43 +1939,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593316</v>
+        <v>593507</v>
       </c>
       <c r="R13" t="n">
-        <v>7183542</v>
+        <v>7183619</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515907</v>
+        <v>121515903</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,39 +2055,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593287</v>
+        <v>593507</v>
       </c>
       <c r="R14" t="n">
-        <v>7183515</v>
+        <v>7183619</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2124,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515903</v>
+        <v>121515898</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,21 +2167,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2201,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593507</v>
+        <v>593511</v>
       </c>
       <c r="R15" t="n">
-        <v>7183619</v>
+        <v>7183603</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2236,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515909</v>
+        <v>121515896</v>
       </c>
       <c r="B16" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,34 +2279,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593312</v>
+        <v>593511</v>
       </c>
       <c r="R16" t="n">
-        <v>7183526</v>
+        <v>7183604</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2348,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515902</v>
+        <v>121515913</v>
       </c>
       <c r="B17" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,21 +2396,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2425,10 +2420,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593507</v>
+        <v>593494</v>
       </c>
       <c r="R17" t="n">
-        <v>7183619</v>
+        <v>7183555</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515899</v>
+        <v>121515904</v>
       </c>
       <c r="B18" t="n">
-        <v>97067</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,38 +2504,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593510</v>
+        <v>593316</v>
       </c>
       <c r="R18" t="n">
-        <v>7183602</v>
+        <v>7183542</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515912</v>
+        <v>121515911</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593492</v>
+        <v>593312</v>
       </c>
       <c r="R2" t="n">
-        <v>7183557</v>
+        <v>7183527</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515895</v>
+        <v>121515905</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593515</v>
+        <v>593297</v>
       </c>
       <c r="R3" t="n">
-        <v>7183592</v>
+        <v>7183540</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515900</v>
+        <v>121515907</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593510</v>
+        <v>593287</v>
       </c>
       <c r="R4" t="n">
-        <v>7183600</v>
+        <v>7183515</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515902</v>
+        <v>121515903</v>
       </c>
       <c r="B5" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1133,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515906</v>
+        <v>121515900</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593300</v>
+        <v>593510</v>
       </c>
       <c r="R6" t="n">
-        <v>7183536</v>
+        <v>7183600</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515894</v>
+        <v>121515896</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1290,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593555</v>
+        <v>593511</v>
       </c>
       <c r="R7" t="n">
-        <v>7183567</v>
+        <v>7183604</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515899</v>
+        <v>121515895</v>
       </c>
       <c r="B8" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,38 +1369,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593510</v>
+        <v>593515</v>
       </c>
       <c r="R8" t="n">
-        <v>7183602</v>
+        <v>7183592</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515911</v>
+        <v>121515894</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,34 +1490,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593312</v>
+        <v>593555</v>
       </c>
       <c r="R9" t="n">
-        <v>7183527</v>
+        <v>7183567</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1591,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515905</v>
+        <v>121515898</v>
       </c>
       <c r="B10" t="n">
         <v>90746</v>
@@ -1626,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593297</v>
+        <v>593511</v>
       </c>
       <c r="R10" t="n">
-        <v>7183540</v>
+        <v>7183603</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515909</v>
+        <v>121515906</v>
       </c>
       <c r="B11" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593312</v>
+        <v>593300</v>
       </c>
       <c r="R11" t="n">
-        <v>7183526</v>
+        <v>7183536</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515907</v>
+        <v>121515909</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,39 +1831,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593287</v>
+        <v>593312</v>
       </c>
       <c r="R12" t="n">
-        <v>7183515</v>
+        <v>7183526</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2039,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515903</v>
+        <v>121515902</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,21 +2055,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515898</v>
+        <v>121515904</v>
       </c>
       <c r="B15" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,34 +2167,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593511</v>
+        <v>593316</v>
       </c>
       <c r="R15" t="n">
-        <v>7183603</v>
+        <v>7183542</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515896</v>
+        <v>121515899</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>97067</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,43 +2280,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593511</v>
+        <v>593510</v>
       </c>
       <c r="R16" t="n">
-        <v>7183604</v>
+        <v>7183602</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515913</v>
+        <v>121515912</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,34 +2396,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593494</v>
+        <v>593492</v>
       </c>
       <c r="R17" t="n">
-        <v>7183555</v>
+        <v>7183557</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2492,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515904</v>
+        <v>121515913</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,39 +2513,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593316</v>
+        <v>593494</v>
       </c>
       <c r="R18" t="n">
-        <v>7183542</v>
+        <v>7183555</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 35393-2024 artfynd.xlsx
+++ b/artfynd/A 35393-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515911</v>
+        <v>121515903</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593312</v>
+        <v>593507</v>
       </c>
       <c r="R2" t="n">
-        <v>7183527</v>
+        <v>7183619</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515905</v>
+        <v>121515899</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593297</v>
+        <v>593510</v>
       </c>
       <c r="R3" t="n">
-        <v>7183540</v>
+        <v>7183602</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515903</v>
+        <v>121515909</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593507</v>
+        <v>593312</v>
       </c>
       <c r="R5" t="n">
-        <v>7183619</v>
+        <v>7183526</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515900</v>
+        <v>121515911</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593510</v>
+        <v>593312</v>
       </c>
       <c r="R6" t="n">
-        <v>7183600</v>
+        <v>7183527</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515896</v>
+        <v>121515901</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>77957</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,43 +1252,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593511</v>
+        <v>593507</v>
       </c>
       <c r="R7" t="n">
-        <v>7183604</v>
+        <v>7183619</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515895</v>
+        <v>121515898</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,39 +1368,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593515</v>
+        <v>593511</v>
       </c>
       <c r="R8" t="n">
-        <v>7183592</v>
+        <v>7183603</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1474,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515894</v>
+        <v>121515912</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,16 +1480,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1510,7 +1500,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1519,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593555</v>
+        <v>593492</v>
       </c>
       <c r="R9" t="n">
-        <v>7183567</v>
+        <v>7183557</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515898</v>
+        <v>121515913</v>
       </c>
       <c r="B10" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1597,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593511</v>
+        <v>593494</v>
       </c>
       <c r="R10" t="n">
-        <v>7183603</v>
+        <v>7183555</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1815,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515909</v>
+        <v>121515900</v>
       </c>
       <c r="B12" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593312</v>
+        <v>593510</v>
       </c>
       <c r="R12" t="n">
-        <v>7183526</v>
+        <v>7183600</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515901</v>
+        <v>121515904</v>
       </c>
       <c r="B13" t="n">
-        <v>77957</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,38 +1929,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593507</v>
+        <v>593316</v>
       </c>
       <c r="R13" t="n">
-        <v>7183619</v>
+        <v>7183542</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2151,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515904</v>
+        <v>121515894</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2187,7 +2182,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2196,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593316</v>
+        <v>593555</v>
       </c>
       <c r="R15" t="n">
-        <v>7183542</v>
+        <v>7183567</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515899</v>
+        <v>121515905</v>
       </c>
       <c r="B16" t="n">
-        <v>97067</v>
+        <v>90746</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,25 +2275,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2308,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593510</v>
+        <v>593297</v>
       </c>
       <c r="R16" t="n">
-        <v>7183602</v>
+        <v>7183540</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,7 +2375,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515912</v>
+        <v>121515895</v>
       </c>
       <c r="B17" t="n">
         <v>57373</v>
@@ -2416,7 +2411,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2425,10 +2420,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593492</v>
+        <v>593515</v>
       </c>
       <c r="R17" t="n">
-        <v>7183557</v>
+        <v>7183592</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515913</v>
+        <v>121515896</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,34 +2508,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593494</v>
+        <v>593511</v>
       </c>
       <c r="R18" t="n">
-        <v>7183555</v>
+        <v>7183604</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
